--- a/E2E_Test_Report_PlantCareAI.xlsx
+++ b/E2E_Test_Report_PlantCareAI.xlsx
@@ -621,7 +621,7 @@
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>53.02 req/sec</t>
+          <t>35.04 req/sec</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -687,7 +687,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>33.8 ms</t>
+          <t>32.9 ms</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>40.9 ms</t>
+          <t>39.9 ms</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>53.02 req/sec</t>
+          <t>35.04 req/sec</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>54.22%</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>967.75 ms</t>
+          <t>333.93 ms</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>2106.25 ms</t>
+          <t>6370.36 ms</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>14462.96 ms</t>
+          <t>12345.9 ms</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>3437.83 ms</t>
+          <t>11211.69 ms</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="H2" s="15" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="H3" s="18" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="H4" s="15" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="H7" s="18" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="H26" s="15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="H30" s="15" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="H32" s="15" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="H51" s="18" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="H53" s="18" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="H55" s="18" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="H57" s="18" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="H59" s="18" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="H60" s="15" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="H61" s="18" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="H63" s="18" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="H65" s="18" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="H66" s="15" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="H67" s="18" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="H68" s="15" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="H69" s="18" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="H71" s="18" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="H73" s="18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="H75" s="18" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="H76" s="15" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="H77" s="18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="H78" s="15" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="H79" s="18" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="H80" s="15" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="H81" s="18" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="H82" s="15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="H83" s="18" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84">
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="H84" s="15" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H85" s="18" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="H86" s="15" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="H87" s="18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="H88" s="15" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="H89" s="18" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="H90" s="15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="H91" s="18" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="H92" s="15" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="H93" s="18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="H94" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="H95" s="18" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="H96" s="15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="H97" s="18" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="H98" s="15" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="H99" s="18" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="H100" s="15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="H101" s="18" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="H102" s="15" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="H103" s="18" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="H104" s="15" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="H106" s="15" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="H107" s="18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108">
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="H109" s="18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="H111" s="18" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="H112" s="15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="H113" s="18" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="H114" s="15" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="H115" s="18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="H117" s="18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118">
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H119" s="18" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="H121" s="18" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="H123" s="18" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="124">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="125">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="H125" s="18" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="H126" s="15" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="H127" s="18" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="H128" s="15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="H129" s="18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="H130" s="15" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="H131" s="18" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="H132" s="15" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="H133" s="18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="H134" s="15" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="H135" s="18" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="H136" s="15" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="137">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="H137" s="18" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="H138" s="15" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="H139" s="18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H140" s="15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="H142" s="15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="H143" s="18" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="144">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="H144" s="15" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="145">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="H145" s="18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="H146" s="15" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147">
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="H147" s="18" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="148">
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="H148" s="15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="H149" s="18" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="H150" s="15" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="H151" s="18" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="H152" s="15" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="H153" s="18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="H154" s="15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="H155" s="18" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="156">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="H156" s="15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="H157" s="18" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="H158" s="15" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="159">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="H159" s="18" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="H160" s="15" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="H161" s="18" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="H162" s="15" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="163">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="H163" s="18" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="H164" s="15" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="165">
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="H165" s="18" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="H166" s="15" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="167">
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="H167" s="18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="168">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="H168" s="15" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="169">
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="H169" s="18" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="170">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="H170" s="15" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171">
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="H171" s="18" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="H172" s="15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="H173" s="18" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174">
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="H174" s="15" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="175">
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="H175" s="18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="H176" s="15" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="H177" s="18" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="178">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="H178" s="15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179">
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="H180" s="15" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181">
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="H181" s="18" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182">
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="H182" s="15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="H183" s="18" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="184">
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="H184" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185">
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="H185" s="18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="186">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="H187" s="18" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="188">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="H188" s="15" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189">
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="H189" s="18" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="H190" s="15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="H191" s="18" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="192">
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="H192" s="15" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="193">
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="H193" s="18" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194">
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="H194" s="15" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="195">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="H195" s="18" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="196">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="H196" s="15" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="197">
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="198">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="H198" s="15" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199">
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="H199" s="18" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="200">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="H200" s="15" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="H201" s="18" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="H202" s="15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="203">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="H204" s="15" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="206">
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="H206" s="15" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="207">
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="208">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="H208" s="15" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="209">
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="210">
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="H210" s="15" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212">
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="H212" s="15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="H213" s="18" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214">
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="H214" s="15" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="215">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="H215" s="18" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216">
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="H216" s="15" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="217">
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="H217" s="18" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="218">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="H218" s="15" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219">
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="H219" s="18" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="220">
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="H220" s="15" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221">
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="H221" s="18" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222">
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="H222" s="15" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="223">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="H223" s="18" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224">
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="H224" s="15" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="225">
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="H225" s="18" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="226">
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="H226" s="15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="H227" s="18" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="228">
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="H228" s="15" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229">
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="H229" s="18" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="230">
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="H230" s="15" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="231">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="H232" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="233">
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="H233" s="18" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234">
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="H235" s="18" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="236">
@@ -10831,7 +10831,7 @@
         </is>
       </c>
       <c r="H236" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237">
@@ -10873,7 +10873,7 @@
         </is>
       </c>
       <c r="H237" s="18" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="H238" s="15" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
     </row>
     <row r="239">
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="H239" s="18" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="240">
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="H240" s="15" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="241">
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="H241" s="18" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242">
@@ -11083,7 +11083,7 @@
         </is>
       </c>
       <c r="H242" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="243">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="H244" s="15" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="245">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="H245" s="18" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="H246" s="15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247">
@@ -11293,7 +11293,7 @@
         </is>
       </c>
       <c r="H247" s="18" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="H249" s="18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250">
@@ -11419,7 +11419,7 @@
         </is>
       </c>
       <c r="H250" s="15" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251">
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="H251" s="18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="H252" s="15" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="253">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="H253" s="18" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="254">
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="H254" s="15" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="H255" s="18" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="256">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="H256" s="15" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="257">
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="H257" s="18" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="258">
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="H258" s="15" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="259">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="H259" s="18" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="260">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="H260" s="15" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="261">
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="H261" s="18" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="262">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="H262" s="15" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="263">
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="H263" s="18" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="264">
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="H264" s="15" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="265">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="H265" s="18" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266">
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="H266" s="15" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="267">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="H267" s="18" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="268">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="H268" s="15" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269">
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="H269" s="18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="270">
@@ -12259,7 +12259,7 @@
         </is>
       </c>
       <c r="H270" s="15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="271">
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="H271" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="272">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="H272" s="15" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="H273" s="18" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="274">
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="H274" s="15" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="275">
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="H275" s="18" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276">
@@ -12511,7 +12511,7 @@
         </is>
       </c>
       <c r="H276" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="277">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="H277" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="278">
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="H278" s="15" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279">
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="H279" s="18" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="280">
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="H280" s="15" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="281">
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="H281" s="18" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="282">
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="H282" s="15" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="283">
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="H283" s="18" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="284">
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="H284" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="285">
@@ -12889,7 +12889,7 @@
         </is>
       </c>
       <c r="H285" s="18" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286">
@@ -12931,7 +12931,7 @@
         </is>
       </c>
       <c r="H286" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="287">
@@ -12973,7 +12973,7 @@
         </is>
       </c>
       <c r="H287" s="18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="288">
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="H288" s="15" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="289">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H289" s="18" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="290">
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="H290" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291">
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="H291" s="18" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="292">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="H292" s="15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="293">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="H293" s="18" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="294">
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="H294" s="15" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295">
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="H295" s="18" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="296">
@@ -13351,7 +13351,7 @@
         </is>
       </c>
       <c r="H296" s="15" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="297">
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="H297" s="18" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="298">
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="H298" s="15" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="299">
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="H299" s="18" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="H300" s="15" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="301">
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="H301" s="18" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="H2" s="15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="H3" s="18" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="H4" s="15" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -13842,7 +13842,7 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="H7" s="18" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -13971,7 +13971,7 @@
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -14186,7 +14186,7 @@
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -14314,7 +14314,7 @@
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -14356,7 +14356,7 @@
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -14650,7 +14650,7 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="H26" s="15" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -14776,7 +14776,7 @@
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="H30" s="15" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
@@ -14902,7 +14902,7 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="H32" s="15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -14986,7 +14986,7 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -15112,7 +15112,7 @@
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
@@ -15358,7 +15358,7 @@
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
@@ -15399,7 +15399,7 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -15440,7 +15440,7 @@
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
@@ -15563,7 +15563,7 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48">
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -15645,7 +15645,7 @@
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -15727,7 +15727,7 @@
         </is>
       </c>
       <c r="H51" s="18" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -15768,7 +15768,7 @@
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="H53" s="18" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -15850,7 +15850,7 @@
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55">
@@ -15891,7 +15891,7 @@
         </is>
       </c>
       <c r="H55" s="18" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -15932,7 +15932,7 @@
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="H57" s="18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="H59" s="18" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
@@ -16096,7 +16096,7 @@
         </is>
       </c>
       <c r="H60" s="15" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="H61" s="18" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63">
@@ -16219,7 +16219,7 @@
         </is>
       </c>
       <c r="H63" s="18" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="H65" s="18" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="H66" s="15" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67">
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="H67" s="18" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="H68" s="15" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69">
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="H69" s="18" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70">
@@ -16506,7 +16506,7 @@
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71">
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="H71" s="18" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="H73" s="18" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
@@ -16715,7 +16715,7 @@
         </is>
       </c>
       <c r="H75" s="18" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="H76" s="15" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="H78" s="15" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -16883,7 +16883,7 @@
         </is>
       </c>
       <c r="H79" s="18" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="H80" s="15" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="H81" s="18" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82">
@@ -17009,7 +17009,7 @@
         </is>
       </c>
       <c r="H82" s="15" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
@@ -17051,7 +17051,7 @@
         </is>
       </c>
       <c r="H83" s="18" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="H84" s="15" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85">
@@ -17135,7 +17135,7 @@
         </is>
       </c>
       <c r="H85" s="18" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="H86" s="15" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
@@ -17219,7 +17219,7 @@
         </is>
       </c>
       <c r="H87" s="18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="H88" s="15" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="H89" s="18" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="H90" s="15" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91">
@@ -17387,7 +17387,7 @@
         </is>
       </c>
       <c r="H91" s="18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="H92" s="15" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="H93" s="18" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
@@ -17513,7 +17513,7 @@
         </is>
       </c>
       <c r="H94" s="15" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -17555,7 +17555,7 @@
         </is>
       </c>
       <c r="H95" s="18" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="H96" s="15" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97">
@@ -17639,7 +17639,7 @@
         </is>
       </c>
       <c r="H97" s="18" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98">
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="H98" s="15" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99">
@@ -17723,7 +17723,7 @@
         </is>
       </c>
       <c r="H99" s="18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100">
@@ -17765,7 +17765,7 @@
         </is>
       </c>
       <c r="H100" s="15" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="H101" s="18" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102">
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="H102" s="15" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103">
@@ -17891,7 +17891,7 @@
         </is>
       </c>
       <c r="H103" s="18" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104">
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="H104" s="15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105">
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="H105" s="18" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="106">
@@ -18017,7 +18017,7 @@
         </is>
       </c>
       <c r="H106" s="15" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
@@ -18059,7 +18059,7 @@
         </is>
       </c>
       <c r="H107" s="18" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108">
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="H108" s="15" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109">
@@ -18143,7 +18143,7 @@
         </is>
       </c>
       <c r="H109" s="18" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
@@ -18185,7 +18185,7 @@
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111">
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="H111" s="18" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112">
@@ -18269,7 +18269,7 @@
         </is>
       </c>
       <c r="H112" s="15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
@@ -18311,7 +18311,7 @@
         </is>
       </c>
       <c r="H113" s="18" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114">
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="H114" s="15" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="H115" s="18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116">
@@ -18437,7 +18437,7 @@
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117">
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="H117" s="18" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="118">
@@ -18521,7 +18521,7 @@
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119">
@@ -18563,7 +18563,7 @@
         </is>
       </c>
       <c r="H119" s="18" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="121">
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="H121" s="18" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122">
@@ -18689,7 +18689,7 @@
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="123">
@@ -18731,7 +18731,7 @@
         </is>
       </c>
       <c r="H123" s="18" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="H125" s="18" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="126">
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="H126" s="15" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127">
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="H127" s="18" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="128">
@@ -18941,7 +18941,7 @@
         </is>
       </c>
       <c r="H128" s="15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
@@ -18983,7 +18983,7 @@
         </is>
       </c>
       <c r="H129" s="18" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130">
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="H130" s="15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="131">
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="H131" s="18" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="H132" s="15" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133">
@@ -19151,7 +19151,7 @@
         </is>
       </c>
       <c r="H133" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134">
@@ -19193,7 +19193,7 @@
         </is>
       </c>
       <c r="H134" s="15" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="H135" s="18" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136">
@@ -19277,7 +19277,7 @@
         </is>
       </c>
       <c r="H136" s="15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137">
@@ -19319,7 +19319,7 @@
         </is>
       </c>
       <c r="H137" s="18" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="H138" s="15" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="139">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="H139" s="18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140">
@@ -19445,7 +19445,7 @@
         </is>
       </c>
       <c r="H140" s="15" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="H141" s="18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="H142" s="15" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
@@ -19569,7 +19569,7 @@
         </is>
       </c>
       <c r="H143" s="18" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144">
@@ -19610,7 +19610,7 @@
         </is>
       </c>
       <c r="H144" s="15" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145">
@@ -19651,7 +19651,7 @@
         </is>
       </c>
       <c r="H145" s="18" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="146">
@@ -19692,7 +19692,7 @@
         </is>
       </c>
       <c r="H146" s="15" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
     </row>
     <row r="147">
@@ -19733,7 +19733,7 @@
         </is>
       </c>
       <c r="H147" s="18" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="148">
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="H148" s="15" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149">
@@ -19815,7 +19815,7 @@
         </is>
       </c>
       <c r="H149" s="18" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
@@ -19856,7 +19856,7 @@
         </is>
       </c>
       <c r="H150" s="15" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151">
@@ -19897,7 +19897,7 @@
         </is>
       </c>
       <c r="H151" s="18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152">
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="H152" s="15" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="H153" s="18" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="154">
@@ -20020,7 +20020,7 @@
         </is>
       </c>
       <c r="H154" s="15" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155">
@@ -20061,7 +20061,7 @@
         </is>
       </c>
       <c r="H155" s="18" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="H156" s="15" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157">
@@ -20143,7 +20143,7 @@
         </is>
       </c>
       <c r="H157" s="18" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158">
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="H158" s="15" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159">
@@ -20225,7 +20225,7 @@
         </is>
       </c>
       <c r="H159" s="18" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160">
@@ -20266,7 +20266,7 @@
         </is>
       </c>
       <c r="H160" s="15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161">
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="H161" s="18" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="162">
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="H162" s="15" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="163">
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="H163" s="18" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164">
@@ -20433,7 +20433,7 @@
         </is>
       </c>
       <c r="H164" s="15" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165">
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="H165" s="18" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="166">
@@ -20517,7 +20517,7 @@
         </is>
       </c>
       <c r="H166" s="15" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167">
@@ -20559,7 +20559,7 @@
         </is>
       </c>
       <c r="H167" s="18" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="168">
@@ -20601,7 +20601,7 @@
         </is>
       </c>
       <c r="H168" s="15" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="169">
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="H169" s="18" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170">
@@ -20685,7 +20685,7 @@
         </is>
       </c>
       <c r="H170" s="15" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171">
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="H171" s="18" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172">
@@ -20769,7 +20769,7 @@
         </is>
       </c>
       <c r="H172" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="173">
@@ -20811,7 +20811,7 @@
         </is>
       </c>
       <c r="H173" s="18" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="174">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="H174" s="15" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="175">
@@ -20895,7 +20895,7 @@
         </is>
       </c>
       <c r="H175" s="18" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176">
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="H176" s="15" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177">
@@ -20979,7 +20979,7 @@
         </is>
       </c>
       <c r="H177" s="18" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="178">
@@ -21021,7 +21021,7 @@
         </is>
       </c>
       <c r="H178" s="15" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179">
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="H179" s="18" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180">
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="H180" s="15" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181">
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="H181" s="18" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182">
@@ -21189,7 +21189,7 @@
         </is>
       </c>
       <c r="H182" s="15" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="183">
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="H183" s="18" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184">
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="H184" s="15" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="185">
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="H185" s="18" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="H186" s="15" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187">
@@ -21399,7 +21399,7 @@
         </is>
       </c>
       <c r="H187" s="18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="188">
@@ -21441,7 +21441,7 @@
         </is>
       </c>
       <c r="H188" s="15" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189">
@@ -21483,7 +21483,7 @@
         </is>
       </c>
       <c r="H189" s="18" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190">
@@ -21525,7 +21525,7 @@
         </is>
       </c>
       <c r="H190" s="15" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191">
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="H191" s="18" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192">
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="H192" s="15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="H193" s="18" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="194">
@@ -21693,7 +21693,7 @@
         </is>
       </c>
       <c r="H194" s="15" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="195">
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="H195" s="18" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196">
@@ -21777,7 +21777,7 @@
         </is>
       </c>
       <c r="H196" s="15" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197">
@@ -21819,7 +21819,7 @@
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="198">
@@ -21861,7 +21861,7 @@
         </is>
       </c>
       <c r="H198" s="15" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="199">
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="H199" s="18" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="200">
@@ -21945,7 +21945,7 @@
         </is>
       </c>
       <c r="H200" s="15" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="201">
@@ -21987,7 +21987,7 @@
         </is>
       </c>
       <c r="H201" s="18" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="202">
@@ -22029,7 +22029,7 @@
         </is>
       </c>
       <c r="H202" s="15" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="203">
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204">
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="H204" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205">
@@ -22155,7 +22155,7 @@
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="206">
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="H206" s="15" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="207">
@@ -22239,7 +22239,7 @@
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="208">
@@ -22281,7 +22281,7 @@
         </is>
       </c>
       <c r="H208" s="15" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209">
@@ -22323,7 +22323,7 @@
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
     </row>
     <row r="210">
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="H210" s="15" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212">
@@ -22449,7 +22449,7 @@
         </is>
       </c>
       <c r="H212" s="15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="213">
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="H213" s="18" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="214">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="H214" s="15" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215">
@@ -22575,7 +22575,7 @@
         </is>
       </c>
       <c r="H215" s="18" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216">
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="H216" s="15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="H217" s="18" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218">
@@ -22701,7 +22701,7 @@
         </is>
       </c>
       <c r="H218" s="15" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="219">
@@ -22743,7 +22743,7 @@
         </is>
       </c>
       <c r="H219" s="18" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="220">
@@ -22785,7 +22785,7 @@
         </is>
       </c>
       <c r="H220" s="15" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="221">
@@ -22827,7 +22827,7 @@
         </is>
       </c>
       <c r="H221" s="18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="222">
@@ -22869,7 +22869,7 @@
         </is>
       </c>
       <c r="H222" s="15" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="223">
@@ -22911,7 +22911,7 @@
         </is>
       </c>
       <c r="H223" s="18" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="224">
@@ -22953,7 +22953,7 @@
         </is>
       </c>
       <c r="H224" s="15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="225">
@@ -22995,7 +22995,7 @@
         </is>
       </c>
       <c r="H225" s="18" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
     </row>
     <row r="226">
@@ -23037,7 +23037,7 @@
         </is>
       </c>
       <c r="H226" s="15" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="227">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="H227" s="18" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="228">
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="H228" s="15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="229">
@@ -23163,7 +23163,7 @@
         </is>
       </c>
       <c r="H229" s="18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="230">
@@ -23205,7 +23205,7 @@
         </is>
       </c>
       <c r="H230" s="15" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="231">
@@ -23247,7 +23247,7 @@
         </is>
       </c>
       <c r="H231" s="18" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="232">
@@ -23289,7 +23289,7 @@
         </is>
       </c>
       <c r="H232" s="15" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="233">
@@ -23331,7 +23331,7 @@
         </is>
       </c>
       <c r="H233" s="18" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234">
@@ -23373,7 +23373,7 @@
         </is>
       </c>
       <c r="H234" s="15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="235">
@@ -23415,7 +23415,7 @@
         </is>
       </c>
       <c r="H235" s="18" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="236">
@@ -23457,7 +23457,7 @@
         </is>
       </c>
       <c r="H236" s="15" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="237">
@@ -23499,7 +23499,7 @@
         </is>
       </c>
       <c r="H237" s="18" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="238">
@@ -23541,7 +23541,7 @@
         </is>
       </c>
       <c r="H238" s="15" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239">
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="H239" s="18" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="240">
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="H240" s="15" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="241">
@@ -23667,7 +23667,7 @@
         </is>
       </c>
       <c r="H241" s="18" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="242">
@@ -23709,7 +23709,7 @@
         </is>
       </c>
       <c r="H242" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="243">
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="H243" s="18" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244">
@@ -23793,7 +23793,7 @@
         </is>
       </c>
       <c r="H244" s="15" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245">
@@ -23835,7 +23835,7 @@
         </is>
       </c>
       <c r="H245" s="18" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246">
@@ -23877,7 +23877,7 @@
         </is>
       </c>
       <c r="H246" s="15" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="247">
@@ -23919,7 +23919,7 @@
         </is>
       </c>
       <c r="H247" s="18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="248">
@@ -23961,7 +23961,7 @@
         </is>
       </c>
       <c r="H248" s="15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="249">
@@ -24003,7 +24003,7 @@
         </is>
       </c>
       <c r="H249" s="18" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250">
@@ -24045,7 +24045,7 @@
         </is>
       </c>
       <c r="H250" s="15" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251">
@@ -24087,7 +24087,7 @@
         </is>
       </c>
       <c r="H251" s="18" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="252">
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="H253" s="18" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254">
@@ -24213,7 +24213,7 @@
         </is>
       </c>
       <c r="H254" s="15" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="255">
@@ -24255,7 +24255,7 @@
         </is>
       </c>
       <c r="H255" s="18" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="256">
@@ -24297,7 +24297,7 @@
         </is>
       </c>
       <c r="H256" s="15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="257">
@@ -24339,7 +24339,7 @@
         </is>
       </c>
       <c r="H257" s="18" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258">
@@ -24381,7 +24381,7 @@
         </is>
       </c>
       <c r="H258" s="15" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259">
@@ -24423,7 +24423,7 @@
         </is>
       </c>
       <c r="H259" s="18" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="260">
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="H261" s="18" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="262">
@@ -24549,7 +24549,7 @@
         </is>
       </c>
       <c r="H262" s="15" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="263">
@@ -24591,7 +24591,7 @@
         </is>
       </c>
       <c r="H263" s="18" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264">
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="H264" s="15" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="265">
@@ -24675,7 +24675,7 @@
         </is>
       </c>
       <c r="H265" s="18" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="266">
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="H266" s="15" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="267">
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="H267" s="18" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="268">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="H268" s="15" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269">
@@ -24843,7 +24843,7 @@
         </is>
       </c>
       <c r="H269" s="18" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="270">
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="H270" s="15" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="271">
@@ -24927,7 +24927,7 @@
         </is>
       </c>
       <c r="H271" s="18" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="272">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="H272" s="15" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="273">
@@ -25011,7 +25011,7 @@
         </is>
       </c>
       <c r="H273" s="18" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="274">
@@ -25053,7 +25053,7 @@
         </is>
       </c>
       <c r="H274" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="H275" s="18" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="276">
@@ -25137,7 +25137,7 @@
         </is>
       </c>
       <c r="H276" s="15" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="277">
@@ -25179,7 +25179,7 @@
         </is>
       </c>
       <c r="H277" s="18" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="H278" s="15" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="279">
@@ -25263,7 +25263,7 @@
         </is>
       </c>
       <c r="H279" s="18" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="280">
@@ -25305,7 +25305,7 @@
         </is>
       </c>
       <c r="H280" s="15" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="281">
@@ -25347,7 +25347,7 @@
         </is>
       </c>
       <c r="H281" s="18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="282">
@@ -25389,7 +25389,7 @@
         </is>
       </c>
       <c r="H282" s="15" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="283">
@@ -25431,7 +25431,7 @@
         </is>
       </c>
       <c r="H283" s="18" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284">
@@ -25473,7 +25473,7 @@
         </is>
       </c>
       <c r="H284" s="15" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="285">
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="H285" s="18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="286">
@@ -25557,7 +25557,7 @@
         </is>
       </c>
       <c r="H286" s="15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="287">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="H287" s="18" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="288">
@@ -25641,7 +25641,7 @@
         </is>
       </c>
       <c r="H288" s="15" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="289">
@@ -25683,7 +25683,7 @@
         </is>
       </c>
       <c r="H289" s="18" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="290">
@@ -25725,7 +25725,7 @@
         </is>
       </c>
       <c r="H290" s="15" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="291">
@@ -25767,7 +25767,7 @@
         </is>
       </c>
       <c r="H291" s="18" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292">
@@ -25809,7 +25809,7 @@
         </is>
       </c>
       <c r="H292" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="293">
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="H293" s="18" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="294">
@@ -25893,7 +25893,7 @@
         </is>
       </c>
       <c r="H294" s="15" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295">
@@ -25935,7 +25935,7 @@
         </is>
       </c>
       <c r="H295" s="18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="296">
@@ -25977,7 +25977,7 @@
         </is>
       </c>
       <c r="H296" s="15" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="297">
@@ -26019,7 +26019,7 @@
         </is>
       </c>
       <c r="H297" s="18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="298">
@@ -26061,7 +26061,7 @@
         </is>
       </c>
       <c r="H298" s="15" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="299">
@@ -26103,7 +26103,7 @@
         </is>
       </c>
       <c r="H299" s="18" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="300">
@@ -26145,7 +26145,7 @@
         </is>
       </c>
       <c r="H300" s="15" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="301">
@@ -26187,7 +26187,7 @@
         </is>
       </c>
       <c r="H301" s="18" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
